--- a/output/pdf_financials_xlsx/LUNR.xlsx
+++ b/output/pdf_financials_xlsx/LUNR.xlsx
@@ -464,10 +464,8 @@
           <t>Revenue</t>
         </is>
       </c>
-      <c r="B4" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B4" s="3" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="5">
@@ -476,10 +474,8 @@
           <t xml:space="preserve">  Cost of Goods Sold</t>
         </is>
       </c>
-      <c r="B5" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B5" s="3" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="6">
@@ -488,10 +484,8 @@
           <t>Gross Profit</t>
         </is>
       </c>
-      <c r="B6" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B6" s="3" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="7">
@@ -500,10 +494,8 @@
           <t xml:space="preserve">  Selling, General, &amp; Admin. Expense</t>
         </is>
       </c>
-      <c r="B7" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B7" s="3" t="n">
+        <v>0.059385</v>
       </c>
     </row>
     <row r="8">
@@ -512,10 +504,8 @@
           <t xml:space="preserve">  Research &amp; Development</t>
         </is>
       </c>
-      <c r="B8" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B8" s="3" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="9">
@@ -524,10 +514,8 @@
           <t xml:space="preserve">  Other Operating Expense</t>
         </is>
       </c>
-      <c r="B9" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B9" s="3" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="10">
@@ -536,10 +524,8 @@
           <t xml:space="preserve">  Total Operating Expense</t>
         </is>
       </c>
-      <c r="B10" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B10" s="3" t="n">
+        <v>0.059385</v>
       </c>
     </row>
     <row r="11">
@@ -548,10 +534,8 @@
           <t>Operating Income</t>
         </is>
       </c>
-      <c r="B11" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B11" s="3" t="n">
+        <v>-0.059385</v>
       </c>
     </row>
     <row r="12">
@@ -560,10 +544,8 @@
           <t xml:space="preserve">    Interest Income</t>
         </is>
       </c>
-      <c r="B12" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B12" s="3" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="13">
@@ -572,10 +554,8 @@
           <t xml:space="preserve">    Interest Expense</t>
         </is>
       </c>
-      <c r="B13" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B13" s="3" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="14">
@@ -584,10 +564,8 @@
           <t xml:space="preserve">  Net Interest Income</t>
         </is>
       </c>
-      <c r="B14" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B14" s="3" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="15">
@@ -596,10 +574,8 @@
           <t xml:space="preserve">  Other Income (Expense)</t>
         </is>
       </c>
-      <c r="B15" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B15" s="3" t="n">
+        <v>0.009686</v>
       </c>
     </row>
     <row r="16">
@@ -608,10 +584,8 @@
           <t>Pretax Income</t>
         </is>
       </c>
-      <c r="B16" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B16" s="3" t="n">
+        <v>0.47824</v>
       </c>
     </row>
     <row r="17">
@@ -620,10 +594,8 @@
           <t xml:space="preserve">  Tax Provision</t>
         </is>
       </c>
-      <c r="B17" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B17" s="3" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="18">
@@ -656,10 +628,8 @@
           <t xml:space="preserve">    Net Income (Continuing Operations)</t>
         </is>
       </c>
-      <c r="B20" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B20" s="3" t="n">
+        <v>0.47824</v>
       </c>
     </row>
     <row r="21">
@@ -668,10 +638,8 @@
           <t xml:space="preserve">    Net Income (Discontinued Operations)</t>
         </is>
       </c>
-      <c r="B21" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B21" s="3" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="22">
@@ -680,10 +648,8 @@
           <t xml:space="preserve">  Other Income (Minority Interest)</t>
         </is>
       </c>
-      <c r="B22" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B22" s="3" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="23">
@@ -712,10 +678,8 @@
           <t>EPS (Diluted)</t>
         </is>
       </c>
-      <c r="B25" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B25" s="3" t="n">
+        <v>0.02</v>
       </c>
     </row>
     <row r="26">
@@ -724,10 +688,8 @@
           <t>Shares Outstanding (Diluted Average)</t>
         </is>
       </c>
-      <c r="B26" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B26" s="3" t="n">
+        <v>23.912</v>
       </c>
     </row>
     <row r="27">
@@ -736,10 +698,8 @@
           <t>EBIT</t>
         </is>
       </c>
-      <c r="B27" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B27" s="3" t="n">
+        <v>0.47824</v>
       </c>
     </row>
     <row r="28">
@@ -748,10 +708,8 @@
           <t xml:space="preserve">  Depreciation, Depletion and Amortization</t>
         </is>
       </c>
-      <c r="B28" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B28" s="3" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="29">
@@ -760,10 +718,8 @@
           <t>EBITDA</t>
         </is>
       </c>
-      <c r="B29" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B29" s="3" t="n">
+        <v>0.47824</v>
       </c>
     </row>
     <row r="30">
@@ -784,10 +740,8 @@
           <t>Tax Rate %</t>
         </is>
       </c>
-      <c r="B31" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B31" s="3" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="32">
@@ -815,10 +769,8 @@
           <t xml:space="preserve">    Cash and Cash Equivalents</t>
         </is>
       </c>
-      <c r="B34" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B34" s="3" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="35">
@@ -827,10 +779,8 @@
           <t xml:space="preserve">    Marketable Securities</t>
         </is>
       </c>
-      <c r="B35" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B35" s="3" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="36">
@@ -839,10 +789,8 @@
           <t xml:space="preserve">  Cash, Cash Equivalents, Marketable Securities</t>
         </is>
       </c>
-      <c r="B36" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B36" s="3" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="37">
@@ -851,10 +799,8 @@
           <t xml:space="preserve">    Accounts Receivable</t>
         </is>
       </c>
-      <c r="B37" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B37" s="3" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="38">
@@ -863,10 +809,8 @@
           <t xml:space="preserve">    Notes Receivable</t>
         </is>
       </c>
-      <c r="B38" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B38" s="3" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="39">
@@ -875,10 +819,8 @@
           <t xml:space="preserve">    Loans Receivable</t>
         </is>
       </c>
-      <c r="B39" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B39" s="3" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="40">
@@ -887,10 +829,8 @@
           <t xml:space="preserve">    Other Current Receivables</t>
         </is>
       </c>
-      <c r="B40" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B40" s="3" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="41">
@@ -899,10 +839,8 @@
           <t xml:space="preserve">  Total Receivables</t>
         </is>
       </c>
-      <c r="B41" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B41" s="3" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="42">
@@ -911,10 +849,8 @@
           <t xml:space="preserve">    Inventories, Raw Materials &amp; Components</t>
         </is>
       </c>
-      <c r="B42" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B42" s="3" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="43">
@@ -923,10 +859,8 @@
           <t xml:space="preserve">    Inventories, Work In Process</t>
         </is>
       </c>
-      <c r="B43" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B43" s="3" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="44">
@@ -935,10 +869,8 @@
           <t xml:space="preserve">    Inventories, Inventories Adjustments</t>
         </is>
       </c>
-      <c r="B44" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B44" s="3" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="45">
@@ -947,10 +879,8 @@
           <t xml:space="preserve">    Inventories, Finished Goods</t>
         </is>
       </c>
-      <c r="B45" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B45" s="3" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="46">
@@ -959,10 +889,8 @@
           <t xml:space="preserve">    Inventories, Other</t>
         </is>
       </c>
-      <c r="B46" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B46" s="3" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="47">
@@ -971,10 +899,8 @@
           <t xml:space="preserve">  Total Inventories</t>
         </is>
       </c>
-      <c r="B47" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B47" s="3" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="48">
@@ -983,10 +909,8 @@
           <t xml:space="preserve">  Other Current Assets</t>
         </is>
       </c>
-      <c r="B48" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B48" s="3" t="n">
+        <v>1.426262</v>
       </c>
     </row>
     <row r="49">
@@ -995,10 +919,8 @@
           <t xml:space="preserve">  Total Current Assets</t>
         </is>
       </c>
-      <c r="B49" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B49" s="3" t="n">
+        <v>1.426262</v>
       </c>
     </row>
     <row r="50">
@@ -1007,10 +929,8 @@
           <t xml:space="preserve">  Investments And Advances</t>
         </is>
       </c>
-      <c r="B50" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B50" s="3" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="51">
@@ -1019,10 +939,8 @@
           <t xml:space="preserve">      Land And Improvements</t>
         </is>
       </c>
-      <c r="B51" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B51" s="3" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="52">
@@ -1031,10 +949,8 @@
           <t xml:space="preserve">      Buildings And Improvements</t>
         </is>
       </c>
-      <c r="B52" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B52" s="3" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="53">
@@ -1043,10 +959,8 @@
           <t xml:space="preserve">      Machinery, Furniture, Equipment</t>
         </is>
       </c>
-      <c r="B53" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B53" s="3" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="54">
@@ -1055,10 +969,8 @@
           <t xml:space="preserve">      Construction In Progress</t>
         </is>
       </c>
-      <c r="B54" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B54" s="3" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="55">
@@ -1079,10 +991,8 @@
           <t xml:space="preserve">    Gross Property, Plant and Equipment</t>
         </is>
       </c>
-      <c r="B56" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B56" s="3" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="57">
@@ -1091,10 +1001,8 @@
           <t xml:space="preserve">    Accumulated Depreciation</t>
         </is>
       </c>
-      <c r="B57" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B57" s="3" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="58">
@@ -1103,10 +1011,8 @@
           <t xml:space="preserve">  Property, Plant and Equipment</t>
         </is>
       </c>
-      <c r="B58" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B58" s="3" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="59">
@@ -1115,10 +1021,8 @@
           <t xml:space="preserve">  Intangible Assets</t>
         </is>
       </c>
-      <c r="B59" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B59" s="3" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="60">
@@ -1127,10 +1031,8 @@
           <t xml:space="preserve">    Goodwill</t>
         </is>
       </c>
-      <c r="B60" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B60" s="3" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="61">
@@ -1139,10 +1041,8 @@
           <t xml:space="preserve">  Other Long Term Assets</t>
         </is>
       </c>
-      <c r="B61" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B61" s="3" t="n">
+        <v>1.677848</v>
       </c>
     </row>
     <row r="62">
@@ -1151,10 +1051,8 @@
           <t xml:space="preserve">  Total Long-Term Assets</t>
         </is>
       </c>
-      <c r="B62" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B62" s="3" t="n">
+        <v>1.677848</v>
       </c>
     </row>
     <row r="63">
@@ -1173,10 +1071,8 @@
           <t xml:space="preserve">    Accounts Payable</t>
         </is>
       </c>
-      <c r="B64" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B64" s="3" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="65">
@@ -1185,10 +1081,8 @@
           <t xml:space="preserve">    Total Tax Payable</t>
         </is>
       </c>
-      <c r="B65" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B65" s="3" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="66">
@@ -1197,10 +1091,8 @@
           <t xml:space="preserve">    Other Current Payables</t>
         </is>
       </c>
-      <c r="B66" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B66" s="3" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="67">
@@ -1209,10 +1101,8 @@
           <t xml:space="preserve">    Current Accrued Expense</t>
         </is>
       </c>
-      <c r="B67" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B67" s="3" t="n">
+        <v>0.240469</v>
       </c>
     </row>
     <row r="68">
@@ -1221,10 +1111,8 @@
           <t xml:space="preserve">  Accounts Payable &amp; Accrued Expense</t>
         </is>
       </c>
-      <c r="B68" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B68" s="3" t="n">
+        <v>0.240469</v>
       </c>
     </row>
     <row r="69">
@@ -1233,10 +1121,8 @@
           <t xml:space="preserve">    Short-Term Debt</t>
         </is>
       </c>
-      <c r="B69" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B69" s="3" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="70">
@@ -1245,10 +1131,8 @@
           <t xml:space="preserve">    Short-Term Capital Lease Obligation</t>
         </is>
       </c>
-      <c r="B70" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B70" s="3" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="71">
@@ -1257,10 +1141,8 @@
           <t xml:space="preserve">  Short-Term Debt &amp; Capital Lease Obligation</t>
         </is>
       </c>
-      <c r="B71" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B71" s="3" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="72">
@@ -1269,10 +1151,8 @@
           <t xml:space="preserve">    Current Deferred Revenue</t>
         </is>
       </c>
-      <c r="B72" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B72" s="3" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="73">
@@ -1281,10 +1161,8 @@
           <t xml:space="preserve">    Current Deferred Taxes Liabilities</t>
         </is>
       </c>
-      <c r="B73" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B73" s="3" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="74">
@@ -1293,10 +1171,8 @@
           <t xml:space="preserve">  Deferred Tax And Revenue</t>
         </is>
       </c>
-      <c r="B74" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B74" s="3" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="75">
@@ -1305,10 +1181,8 @@
           <t xml:space="preserve">  Other Current Liabilities</t>
         </is>
       </c>
-      <c r="B75" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B75" s="3" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="76">
@@ -1329,10 +1203,8 @@
           <t xml:space="preserve">    Long-Term Debt</t>
         </is>
       </c>
-      <c r="B77" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B77" s="3" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="78">
@@ -1341,10 +1213,8 @@
           <t xml:space="preserve">    Long-Term Capital Lease Obligation</t>
         </is>
       </c>
-      <c r="B78" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B78" s="3" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="79">
@@ -1353,10 +1223,8 @@
           <t xml:space="preserve">  Long-Term Debt &amp; Capital Lease Obligation</t>
         </is>
       </c>
-      <c r="B79" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B79" s="3" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="80">
@@ -1377,10 +1245,8 @@
           <t xml:space="preserve">  Pension And Retirement Benefit</t>
         </is>
       </c>
-      <c r="B81" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B81" s="3" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="82">
@@ -1389,10 +1255,8 @@
           <t xml:space="preserve">    NonCurrent Deferred Revenue</t>
         </is>
       </c>
-      <c r="B82" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B82" s="3" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="83">
@@ -1401,10 +1265,8 @@
           <t xml:space="preserve">  NonCurrent Deferred Liabilities</t>
         </is>
       </c>
-      <c r="B83" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B83" s="3" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="84">
@@ -1413,10 +1275,8 @@
           <t xml:space="preserve">  NonCurrent Deferred Income Tax</t>
         </is>
       </c>
-      <c r="B84" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B84" s="3" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="85">
@@ -1425,10 +1285,8 @@
           <t xml:space="preserve">  Other Long-Term Liabilities</t>
         </is>
       </c>
-      <c r="B85" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B85" s="3" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="86">
@@ -1459,10 +1317,8 @@
           <t xml:space="preserve">  Common Stock</t>
         </is>
       </c>
-      <c r="B88" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B88" s="3" t="n">
+        <v>3.257318</v>
       </c>
     </row>
     <row r="89">
@@ -1471,10 +1327,8 @@
           <t xml:space="preserve">  Preferred Stock</t>
         </is>
       </c>
-      <c r="B89" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B89" s="3" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="90">
@@ -1493,10 +1347,8 @@
           <t xml:space="preserve">  Accumulated other comprehensive income (loss)</t>
         </is>
       </c>
-      <c r="B91" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B91" s="3" t="n">
+        <v>0.073365</v>
       </c>
     </row>
     <row r="92">
@@ -1515,10 +1367,8 @@
           <t xml:space="preserve">  Treasury Stock</t>
         </is>
       </c>
-      <c r="B93" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B93" s="3" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="94">
@@ -1537,10 +1387,8 @@
           <t xml:space="preserve">  Minority Interest</t>
         </is>
       </c>
-      <c r="B95" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B95" s="3" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="96">
@@ -1549,10 +1397,8 @@
           <t>Total Equity</t>
         </is>
       </c>
-      <c r="B96" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B96" s="3" t="n">
+        <v>2.863641</v>
       </c>
     </row>
     <row r="97">
@@ -1578,10 +1424,8 @@
           <t xml:space="preserve">  Net Income From Continuing Operations</t>
         </is>
       </c>
-      <c r="B99" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B99" s="3" t="n">
+        <v>-0.47824</v>
       </c>
     </row>
     <row r="100">
@@ -1590,10 +1434,8 @@
           <t xml:space="preserve">  Cash Flow Depreciation, Depletion and Amortization</t>
         </is>
       </c>
-      <c r="B100" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B100" s="3" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="101">
@@ -1602,10 +1444,8 @@
           <t xml:space="preserve">    Change In Receivables</t>
         </is>
       </c>
-      <c r="B101" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B101" s="3" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="102">
@@ -1614,10 +1454,8 @@
           <t xml:space="preserve">    Change In Inventory</t>
         </is>
       </c>
-      <c r="B102" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B102" s="3" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="103">
@@ -1626,10 +1464,8 @@
           <t xml:space="preserve">    Change In Prepaid Assets</t>
         </is>
       </c>
-      <c r="B103" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B103" s="3" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="104">
@@ -1638,10 +1474,8 @@
           <t xml:space="preserve">    Change In Payables And Accrued Expense</t>
         </is>
       </c>
-      <c r="B104" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B104" s="3" t="n">
+        <v>0.237557</v>
       </c>
     </row>
     <row r="105">
@@ -1650,10 +1484,8 @@
           <t xml:space="preserve">    Change In Other Working Capital</t>
         </is>
       </c>
-      <c r="B105" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B105" s="3" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="106">
@@ -1662,10 +1494,8 @@
           <t xml:space="preserve">  Change In Working Capital</t>
         </is>
       </c>
-      <c r="B106" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B106" s="3" t="n">
+        <v>-0.260222</v>
       </c>
     </row>
     <row r="107">
@@ -1684,10 +1514,8 @@
           <t xml:space="preserve">  Asset Impairment Charge</t>
         </is>
       </c>
-      <c r="B108" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B108" s="3" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="109">
@@ -1696,10 +1524,8 @@
           <t xml:space="preserve">  Cash from Discontinued Operating Activities</t>
         </is>
       </c>
-      <c r="B109" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B109" s="3" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="110">
@@ -1708,10 +1534,8 @@
           <t xml:space="preserve">  Cash Flow from Others</t>
         </is>
       </c>
-      <c r="B110" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B110" s="3" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="111">
@@ -1720,10 +1544,8 @@
           <t xml:space="preserve">  Purchase Of Property, Plant, Equipment</t>
         </is>
       </c>
-      <c r="B111" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B111" s="3" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="112">
@@ -1732,10 +1554,8 @@
           <t xml:space="preserve">  Sale Of Property, Plant, Equipment</t>
         </is>
       </c>
-      <c r="B112" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B112" s="3" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="113">
@@ -1744,10 +1564,8 @@
           <t xml:space="preserve">  Purchase Of Business</t>
         </is>
       </c>
-      <c r="B113" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B113" s="3" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="114">
@@ -1756,10 +1574,8 @@
           <t xml:space="preserve">  Purchase Of Investment</t>
         </is>
       </c>
-      <c r="B114" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B114" s="3" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="115">
@@ -1768,10 +1584,8 @@
           <t xml:space="preserve">  Sale Of Investment</t>
         </is>
       </c>
-      <c r="B115" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B115" s="3" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="116">
@@ -1780,10 +1594,8 @@
           <t xml:space="preserve">  Net Intangibles Purchase And Sale</t>
         </is>
       </c>
-      <c r="B116" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B116" s="3" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="117">
@@ -1792,10 +1604,8 @@
           <t xml:space="preserve">  Cash From Discontinued Investing Activities</t>
         </is>
       </c>
-      <c r="B117" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B117" s="3" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="118">
@@ -1804,10 +1614,8 @@
           <t xml:space="preserve">  Cash From Other Investing Activities</t>
         </is>
       </c>
-      <c r="B118" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B118" s="3" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="119">
@@ -1826,10 +1634,8 @@
           <t xml:space="preserve">  Issuance of Stock</t>
         </is>
       </c>
-      <c r="B120" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B120" s="3" t="n">
+        <v>0.147095</v>
       </c>
     </row>
     <row r="121">
@@ -1838,10 +1644,8 @@
           <t xml:space="preserve">  Repurchase of Stock</t>
         </is>
       </c>
-      <c r="B121" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B121" s="3" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="122">
@@ -1850,10 +1654,8 @@
           <t xml:space="preserve">  Net Issuance of Preferred Stock</t>
         </is>
       </c>
-      <c r="B122" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B122" s="3" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="123">
@@ -1862,10 +1664,8 @@
           <t xml:space="preserve">    Issuance of Debt</t>
         </is>
       </c>
-      <c r="B123" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B123" s="3" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="124">
@@ -1874,10 +1674,8 @@
           <t xml:space="preserve">    Payments of Debt</t>
         </is>
       </c>
-      <c r="B124" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B124" s="3" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="125">
@@ -1886,10 +1684,8 @@
           <t xml:space="preserve">  Net Issuance of Debt</t>
         </is>
       </c>
-      <c r="B125" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B125" s="3" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="126">
@@ -1898,10 +1694,8 @@
           <t xml:space="preserve">  Cash Flow for Dividends</t>
         </is>
       </c>
-      <c r="B126" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B126" s="3" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="127">
@@ -1922,10 +1716,8 @@
           <t xml:space="preserve">  Other Financing</t>
         </is>
       </c>
-      <c r="B128" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B128" s="3" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="129">
@@ -1944,10 +1736,8 @@
           <t xml:space="preserve">  Beginning Cash Position</t>
         </is>
       </c>
-      <c r="B130" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B130" s="3" t="n">
+        <v>-0.23343</v>
       </c>
     </row>
     <row r="131">
@@ -1956,10 +1746,8 @@
           <t xml:space="preserve">    Effect of Exchange Rate Changes</t>
         </is>
       </c>
-      <c r="B131" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B131" s="3" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="132">
@@ -1968,10 +1756,8 @@
           <t xml:space="preserve">  Net Change in Cash</t>
         </is>
       </c>
-      <c r="B132" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B132" s="3" t="n">
+        <v>1.605883</v>
       </c>
     </row>
     <row r="133">
@@ -1980,10 +1766,8 @@
           <t>Ending Cash Position</t>
         </is>
       </c>
-      <c r="B133" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B133" s="3" t="n">
+        <v>1.372453</v>
       </c>
     </row>
     <row r="134">
@@ -1992,10 +1776,8 @@
           <t>Capital Expenditure</t>
         </is>
       </c>
-      <c r="B134" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B134" s="3" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="135">
@@ -2004,10 +1786,8 @@
           <t>Free Cash Flow</t>
         </is>
       </c>
-      <c r="B135" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B135" s="3" t="n">
+        <v>0</v>
       </c>
     </row>
   </sheetData>
@@ -2021,7 +1801,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E86"/>
+  <dimension ref="A1:E47"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="16" customWidth="1" min="1" max="1"/>
@@ -2123,7 +1903,11 @@
           <t>Current assets total</t>
         </is>
       </c>
-      <c r="D4" t="inlineStr"/>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>CurrentAssets</t>
+        </is>
+      </c>
       <c r="E4" s="5" t="n">
         <v>1.426262</v>
       </c>
@@ -2190,7 +1974,11 @@
           <t>Trade payables and accrued liabilities</t>
         </is>
       </c>
-      <c r="D7" t="inlineStr"/>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>CurrentAccruedExpenses</t>
+        </is>
+      </c>
       <c r="E7" s="5" t="n">
         <v>0.240469</v>
       </c>
@@ -2311,7 +2099,11 @@
           <t>Accumulated other comprehensive income</t>
         </is>
       </c>
-      <c r="D12" t="inlineStr"/>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>GainsLossesNotAffectingRetainedEarnings</t>
+        </is>
+      </c>
       <c r="E12" s="5" t="n">
         <v>0.073365</v>
       </c>
@@ -2445,7 +2237,11 @@
           <t>Net loss for the period</t>
         </is>
       </c>
-      <c r="D18" t="inlineStr"/>
+      <c r="D18" t="inlineStr">
+        <is>
+          <t>NetIncomeFromContinuingOperations</t>
+        </is>
+      </c>
       <c r="E18" s="5" t="n">
         <v>-0.47824</v>
       </c>
@@ -2533,7 +2329,11 @@
           <t>Trade payables and accrued liabilities</t>
         </is>
       </c>
-      <c r="D22" t="inlineStr"/>
+      <c r="D22" t="inlineStr">
+        <is>
+          <t>ChangeInPayablesAndAccruedExpense</t>
+        </is>
+      </c>
       <c r="E22" s="5" t="n">
         <v>0.237557</v>
       </c>
@@ -2554,7 +2354,11 @@
           <t>Changes in non-cash working capital total</t>
         </is>
       </c>
-      <c r="D23" t="inlineStr"/>
+      <c r="D23" t="inlineStr">
+        <is>
+          <t>ChangeInWorkingCapital</t>
+        </is>
+      </c>
       <c r="E23" s="5" t="n">
         <v>-0.260222</v>
       </c>
@@ -2642,7 +2446,11 @@
           <t>Proceeds from exercises of stock options</t>
         </is>
       </c>
-      <c r="D27" t="inlineStr"/>
+      <c r="D27" t="inlineStr">
+        <is>
+          <t>IssuanceOfCapitalStock</t>
+        </is>
+      </c>
       <c r="E27" s="5" t="n">
         <v>0.147095</v>
       </c>
@@ -2753,7 +2561,11 @@
           <t>Cash, end of the year</t>
         </is>
       </c>
-      <c r="D32" t="inlineStr"/>
+      <c r="D32" t="inlineStr">
+        <is>
+          <t>EndCashPosition</t>
+        </is>
+      </c>
       <c r="E32" s="5" t="n">
         <v>1.372453</v>
       </c>
@@ -2787,17 +2599,17 @@
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>Vancouver, British Columbia</t>
+          <t>General and administration</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>March 16,</t>
+          <t>Listing and filing fees</t>
         </is>
       </c>
       <c r="D34" t="inlineStr"/>
       <c r="E34" s="5" t="n">
-        <v>0.002026</v>
+        <v>0.19726</v>
       </c>
     </row>
     <row r="35">
@@ -2808,17 +2620,21 @@
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>Current assets</t>
+          <t>General and administration</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>Cash</t>
-        </is>
-      </c>
-      <c r="D35" t="inlineStr"/>
+          <t>Office and general</t>
+        </is>
+      </c>
+      <c r="D35" t="inlineStr">
+        <is>
+          <t>SellingGeneralAndAdministration</t>
+        </is>
+      </c>
       <c r="E35" s="5" t="n">
-        <v>1.372453</v>
+        <v>0.048817</v>
       </c>
     </row>
     <row r="36">
@@ -2829,17 +2645,21 @@
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>Current assets</t>
+          <t>General and administration</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>Receivables and other assets</t>
-        </is>
-      </c>
-      <c r="D36" t="inlineStr"/>
+          <t>Professional fees</t>
+        </is>
+      </c>
+      <c r="D36" t="inlineStr">
+        <is>
+          <t>ProfessionalExpenseAndContractServicesExpense</t>
+        </is>
+      </c>
       <c r="E36" s="5" t="n">
-        <v>0.053809</v>
+        <v>0.06268</v>
       </c>
     </row>
     <row r="37">
@@ -2850,17 +2670,17 @@
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>Current assets</t>
+          <t>General and administration</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>Current assets total</t>
+          <t>Promotion and public relations</t>
         </is>
       </c>
       <c r="D37" t="inlineStr"/>
       <c r="E37" s="5" t="n">
-        <v>1.426262</v>
+        <v>0.027489</v>
       </c>
     </row>
     <row r="38">
@@ -2871,17 +2691,17 @@
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>Current assets</t>
+          <t>General and administration</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>Royalty interests 5</t>
+          <t>Salaries and benefits</t>
         </is>
       </c>
       <c r="D38" t="inlineStr"/>
       <c r="E38" s="5" t="n">
-        <v>1.677848</v>
+        <v>0.097507</v>
       </c>
     </row>
     <row r="39">
@@ -2892,17 +2712,17 @@
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>Current assets</t>
+          <t>General and administration</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>Total assets</t>
+          <t>Share-based compensation</t>
         </is>
       </c>
       <c r="D39" t="inlineStr"/>
       <c r="E39" s="5" t="n">
-        <v>3.10411</v>
+        <v>0.024233</v>
       </c>
     </row>
     <row r="40">
@@ -2913,17 +2733,21 @@
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>Current liabilities</t>
+          <t>General and administration</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>Trade payables and accrued liabilities</t>
-        </is>
-      </c>
-      <c r="D40" t="inlineStr"/>
+          <t>Travel</t>
+        </is>
+      </c>
+      <c r="D40" t="inlineStr">
+        <is>
+          <t>SellingGeneralAndAdministration</t>
+        </is>
+      </c>
       <c r="E40" s="5" t="n">
-        <v>0.240469</v>
+        <v>0.010568</v>
       </c>
     </row>
     <row r="41">
@@ -2934,17 +2758,17 @@
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>Current liabilities</t>
+          <t>General and administration</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>Total liabilities</t>
+          <t>Operating loss</t>
         </is>
       </c>
       <c r="D41" t="inlineStr"/>
       <c r="E41" s="5" t="n">
-        <v>0.240469</v>
+        <v>0.468554</v>
       </c>
     </row>
     <row r="42">
@@ -2955,17 +2779,21 @@
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>Shareholders’ equity</t>
+          <t>Other expenses</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>Share capital 6</t>
-        </is>
-      </c>
-      <c r="D42" t="inlineStr"/>
+          <t>Foreign exchange loss</t>
+        </is>
+      </c>
+      <c r="D42" t="inlineStr">
+        <is>
+          <t>OtherIncomeExpense</t>
+        </is>
+      </c>
       <c r="E42" s="5" t="n">
-        <v>3.257318</v>
+        <v>0.009686</v>
       </c>
     </row>
     <row r="43">
@@ -2976,17 +2804,21 @@
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>Shareholders’ equity</t>
+          <t>Other expenses</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>Contributed surplus</t>
-        </is>
-      </c>
-      <c r="D43" t="inlineStr"/>
+          <t>Net loss</t>
+        </is>
+      </c>
+      <c r="D43" t="inlineStr">
+        <is>
+          <t>NetIncome</t>
+        </is>
+      </c>
       <c r="E43" s="5" t="n">
-        <v>0.011198</v>
+        <v>0.47824</v>
       </c>
     </row>
     <row r="44">
@@ -2997,17 +2829,17 @@
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>Shareholders’ equity</t>
+          <t>Other comprehensive (income)</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>Deficit</t>
+          <t>Currency translation adjustment</t>
         </is>
       </c>
       <c r="D44" t="inlineStr"/>
       <c r="E44" s="5" t="n">
-        <v>-0.47824</v>
+        <v>-0.073365</v>
       </c>
     </row>
     <row r="45">
@@ -3018,17 +2850,17 @@
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>Shareholders’ equity</t>
+          <t>Other comprehensive (income)</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>Accumulated other comprehensive income</t>
+          <t>Comprehensive loss</t>
         </is>
       </c>
       <c r="D45" t="inlineStr"/>
       <c r="E45" s="5" t="n">
-        <v>0.073365</v>
+        <v>0.404875</v>
       </c>
     </row>
     <row r="46">
@@ -3039,17 +2871,21 @@
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>Shareholders’ equity</t>
+          <t>Other comprehensive (income)</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>Total shareholders’ equity</t>
-        </is>
-      </c>
-      <c r="D46" t="inlineStr"/>
+          <t>Basic and diluted loss per common share</t>
+        </is>
+      </c>
+      <c r="D46" t="inlineStr">
+        <is>
+          <t>BasicEPS</t>
+        </is>
+      </c>
       <c r="E46" s="5" t="n">
-        <v>2.863641</v>
+        <v>2e-08</v>
       </c>
     </row>
     <row r="47">
@@ -3060,856 +2896,21 @@
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>Shareholders’ equity</t>
+          <t>Other comprehensive (income)</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>Total liabilities and shareholders’ equity</t>
-        </is>
-      </c>
-      <c r="D47" t="inlineStr"/>
+          <t>Weighted average common shares outstanding</t>
+        </is>
+      </c>
+      <c r="D47" t="inlineStr">
+        <is>
+          <t>SharesOutstanding</t>
+        </is>
+      </c>
       <c r="E47" s="5" t="n">
-        <v>3.10411</v>
-      </c>
-    </row>
-    <row r="48">
-      <c r="A48" t="inlineStr">
-        <is>
-          <t>income_statement</t>
-        </is>
-      </c>
-      <c r="B48" t="inlineStr">
-        <is>
-          <t>Shareholders’ equity</t>
-        </is>
-      </c>
-      <c r="C48" t="inlineStr">
-        <is>
-          <t>Arrangement (Note</t>
-        </is>
-      </c>
-      <c r="D48" t="inlineStr"/>
-      <c r="E48" s="5" t="n">
-        <v>2e-06</v>
-      </c>
-    </row>
-    <row r="49">
-      <c r="A49" t="inlineStr">
-        <is>
-          <t>income_statement</t>
-        </is>
-      </c>
-      <c r="B49" t="inlineStr">
-        <is>
-          <t>Shareholders’ equity</t>
-        </is>
-      </c>
-      <c r="C49" t="inlineStr">
-        <is>
-          <t>Commitment (Note</t>
-        </is>
-      </c>
-      <c r="D49" t="inlineStr"/>
-      <c r="E49" s="5" t="n">
-        <v>1e-05</v>
-      </c>
-    </row>
-    <row r="50">
-      <c r="A50" t="inlineStr">
-        <is>
-          <t>income_statement</t>
-        </is>
-      </c>
-      <c r="B50" t="inlineStr">
-        <is>
-          <t>Shareholders’ equity</t>
-        </is>
-      </c>
-      <c r="C50" t="inlineStr">
-        <is>
-          <t>Subsequent event (Notes 6 and</t>
-        </is>
-      </c>
-      <c r="D50" t="inlineStr"/>
-      <c r="E50" s="5" t="n">
-        <v>1.1e-05</v>
-      </c>
-    </row>
-    <row r="51">
-      <c r="A51" t="inlineStr">
-        <is>
-          <t>income_statement</t>
-        </is>
-      </c>
-      <c r="B51" t="inlineStr">
-        <is>
-          <t>General and administration</t>
-        </is>
-      </c>
-      <c r="C51" t="inlineStr">
-        <is>
-          <t>Listing and filing fees</t>
-        </is>
-      </c>
-      <c r="D51" t="inlineStr"/>
-      <c r="E51" s="5" t="n">
-        <v>0.19726</v>
-      </c>
-    </row>
-    <row r="52">
-      <c r="A52" t="inlineStr">
-        <is>
-          <t>income_statement</t>
-        </is>
-      </c>
-      <c r="B52" t="inlineStr">
-        <is>
-          <t>General and administration</t>
-        </is>
-      </c>
-      <c r="C52" t="inlineStr">
-        <is>
-          <t>Office and general</t>
-        </is>
-      </c>
-      <c r="D52" t="inlineStr"/>
-      <c r="E52" s="5" t="n">
-        <v>0.048817</v>
-      </c>
-    </row>
-    <row r="53">
-      <c r="A53" t="inlineStr">
-        <is>
-          <t>income_statement</t>
-        </is>
-      </c>
-      <c r="B53" t="inlineStr">
-        <is>
-          <t>General and administration</t>
-        </is>
-      </c>
-      <c r="C53" t="inlineStr">
-        <is>
-          <t>Professional fees</t>
-        </is>
-      </c>
-      <c r="D53" t="inlineStr">
-        <is>
-          <t>ProfessionalExpenseAndContractServicesExpense</t>
-        </is>
-      </c>
-      <c r="E53" s="5" t="n">
-        <v>0.06268</v>
-      </c>
-    </row>
-    <row r="54">
-      <c r="A54" t="inlineStr">
-        <is>
-          <t>income_statement</t>
-        </is>
-      </c>
-      <c r="B54" t="inlineStr">
-        <is>
-          <t>General and administration</t>
-        </is>
-      </c>
-      <c r="C54" t="inlineStr">
-        <is>
-          <t>Promotion and public relations</t>
-        </is>
-      </c>
-      <c r="D54" t="inlineStr"/>
-      <c r="E54" s="5" t="n">
-        <v>0.027489</v>
-      </c>
-    </row>
-    <row r="55">
-      <c r="A55" t="inlineStr">
-        <is>
-          <t>income_statement</t>
-        </is>
-      </c>
-      <c r="B55" t="inlineStr">
-        <is>
-          <t>General and administration</t>
-        </is>
-      </c>
-      <c r="C55" t="inlineStr">
-        <is>
-          <t>Salaries and benefits</t>
-        </is>
-      </c>
-      <c r="D55" t="inlineStr"/>
-      <c r="E55" s="5" t="n">
-        <v>0.097507</v>
-      </c>
-    </row>
-    <row r="56">
-      <c r="A56" t="inlineStr">
-        <is>
-          <t>income_statement</t>
-        </is>
-      </c>
-      <c r="B56" t="inlineStr">
-        <is>
-          <t>General and administration</t>
-        </is>
-      </c>
-      <c r="C56" t="inlineStr">
-        <is>
-          <t>Share-based compensation</t>
-        </is>
-      </c>
-      <c r="D56" t="inlineStr"/>
-      <c r="E56" s="5" t="n">
-        <v>0.024233</v>
-      </c>
-    </row>
-    <row r="57">
-      <c r="A57" t="inlineStr">
-        <is>
-          <t>income_statement</t>
-        </is>
-      </c>
-      <c r="B57" t="inlineStr">
-        <is>
-          <t>General and administration</t>
-        </is>
-      </c>
-      <c r="C57" t="inlineStr">
-        <is>
-          <t>Travel</t>
-        </is>
-      </c>
-      <c r="D57" t="inlineStr"/>
-      <c r="E57" s="5" t="n">
-        <v>0.010568</v>
-      </c>
-    </row>
-    <row r="58">
-      <c r="A58" t="inlineStr">
-        <is>
-          <t>income_statement</t>
-        </is>
-      </c>
-      <c r="B58" t="inlineStr">
-        <is>
-          <t>General and administration</t>
-        </is>
-      </c>
-      <c r="C58" t="inlineStr">
-        <is>
-          <t>Operating loss</t>
-        </is>
-      </c>
-      <c r="D58" t="inlineStr"/>
-      <c r="E58" s="5" t="n">
-        <v>0.468554</v>
-      </c>
-    </row>
-    <row r="59">
-      <c r="A59" t="inlineStr">
-        <is>
-          <t>income_statement</t>
-        </is>
-      </c>
-      <c r="B59" t="inlineStr">
-        <is>
-          <t>Other expenses</t>
-        </is>
-      </c>
-      <c r="C59" t="inlineStr">
-        <is>
-          <t>Foreign exchange loss</t>
-        </is>
-      </c>
-      <c r="D59" t="inlineStr"/>
-      <c r="E59" s="5" t="n">
-        <v>0.009686</v>
-      </c>
-    </row>
-    <row r="60">
-      <c r="A60" t="inlineStr">
-        <is>
-          <t>income_statement</t>
-        </is>
-      </c>
-      <c r="B60" t="inlineStr">
-        <is>
-          <t>Other expenses</t>
-        </is>
-      </c>
-      <c r="C60" t="inlineStr">
-        <is>
-          <t>Net loss</t>
-        </is>
-      </c>
-      <c r="D60" t="inlineStr">
-        <is>
-          <t>NetIncome</t>
-        </is>
-      </c>
-      <c r="E60" s="5" t="n">
-        <v>0.47824</v>
-      </c>
-    </row>
-    <row r="61">
-      <c r="A61" t="inlineStr">
-        <is>
-          <t>income_statement</t>
-        </is>
-      </c>
-      <c r="B61" t="inlineStr">
-        <is>
-          <t>Other comprehensive (income)</t>
-        </is>
-      </c>
-      <c r="C61" t="inlineStr">
-        <is>
-          <t>Currency translation adjustment</t>
-        </is>
-      </c>
-      <c r="D61" t="inlineStr"/>
-      <c r="E61" s="5" t="n">
-        <v>-0.073365</v>
-      </c>
-    </row>
-    <row r="62">
-      <c r="A62" t="inlineStr">
-        <is>
-          <t>income_statement</t>
-        </is>
-      </c>
-      <c r="B62" t="inlineStr">
-        <is>
-          <t>Other comprehensive (income)</t>
-        </is>
-      </c>
-      <c r="C62" t="inlineStr">
-        <is>
-          <t>Comprehensive loss</t>
-        </is>
-      </c>
-      <c r="D62" t="inlineStr"/>
-      <c r="E62" s="5" t="n">
-        <v>0.404875</v>
-      </c>
-    </row>
-    <row r="63">
-      <c r="A63" t="inlineStr">
-        <is>
-          <t>income_statement</t>
-        </is>
-      </c>
-      <c r="B63" t="inlineStr">
-        <is>
-          <t>Other comprehensive (income)</t>
-        </is>
-      </c>
-      <c r="C63" t="inlineStr">
-        <is>
-          <t>Basic and diluted loss per common share</t>
-        </is>
-      </c>
-      <c r="D63" t="inlineStr">
-        <is>
-          <t>BasicEPS</t>
-        </is>
-      </c>
-      <c r="E63" s="5" t="n">
-        <v>2e-08</v>
-      </c>
-    </row>
-    <row r="64">
-      <c r="A64" t="inlineStr">
-        <is>
-          <t>income_statement</t>
-        </is>
-      </c>
-      <c r="B64" t="inlineStr">
-        <is>
-          <t>Other comprehensive (income)</t>
-        </is>
-      </c>
-      <c r="C64" t="inlineStr">
-        <is>
-          <t>Weighted average common shares outstanding</t>
-        </is>
-      </c>
-      <c r="D64" t="inlineStr">
-        <is>
-          <t>SharesOutstanding</t>
-        </is>
-      </c>
-      <c r="E64" s="5" t="n">
         <v>28.945492</v>
-      </c>
-    </row>
-    <row r="65">
-      <c r="A65" t="inlineStr">
-        <is>
-          <t>income_statement</t>
-        </is>
-      </c>
-      <c r="B65" t="inlineStr">
-        <is>
-          <t>Cash used in operating activities</t>
-        </is>
-      </c>
-      <c r="C65" t="inlineStr">
-        <is>
-          <t>Net loss for the period</t>
-        </is>
-      </c>
-      <c r="D65" t="inlineStr"/>
-      <c r="E65" s="5" t="n">
-        <v>-0.47824</v>
-      </c>
-    </row>
-    <row r="66">
-      <c r="A66" t="inlineStr">
-        <is>
-          <t>income_statement</t>
-        </is>
-      </c>
-      <c r="B66" t="inlineStr">
-        <is>
-          <t>Adjustments for</t>
-        </is>
-      </c>
-      <c r="C66" t="inlineStr">
-        <is>
-          <t>Share-based compensation</t>
-        </is>
-      </c>
-      <c r="D66" t="inlineStr"/>
-      <c r="E66" s="5" t="n">
-        <v>0.024233</v>
-      </c>
-    </row>
-    <row r="67">
-      <c r="A67" t="inlineStr">
-        <is>
-          <t>income_statement</t>
-        </is>
-      </c>
-      <c r="B67" t="inlineStr">
-        <is>
-          <t>Adjustments for</t>
-        </is>
-      </c>
-      <c r="C67" t="inlineStr">
-        <is>
-          <t>Non-cash foreign exchange loss</t>
-        </is>
-      </c>
-      <c r="D67" t="inlineStr"/>
-      <c r="E67" s="5" t="n">
-        <v>0.005307</v>
-      </c>
-    </row>
-    <row r="68">
-      <c r="A68" t="inlineStr">
-        <is>
-          <t>income_statement</t>
-        </is>
-      </c>
-      <c r="B68" t="inlineStr">
-        <is>
-          <t>Changes in non-cash working capital</t>
-        </is>
-      </c>
-      <c r="C68" t="inlineStr">
-        <is>
-          <t>Receivables and other assets</t>
-        </is>
-      </c>
-      <c r="D68" t="inlineStr"/>
-      <c r="E68" s="5" t="n">
-        <v>-0.049079</v>
-      </c>
-    </row>
-    <row r="69">
-      <c r="A69" t="inlineStr">
-        <is>
-          <t>income_statement</t>
-        </is>
-      </c>
-      <c r="B69" t="inlineStr">
-        <is>
-          <t>Changes in non-cash working capital</t>
-        </is>
-      </c>
-      <c r="C69" t="inlineStr">
-        <is>
-          <t>Trade payables and accrued liabilities</t>
-        </is>
-      </c>
-      <c r="D69" t="inlineStr"/>
-      <c r="E69" s="5" t="n">
-        <v>0.237557</v>
-      </c>
-    </row>
-    <row r="70">
-      <c r="A70" t="inlineStr">
-        <is>
-          <t>income_statement</t>
-        </is>
-      </c>
-      <c r="B70" t="inlineStr">
-        <is>
-          <t>Changes in non-cash working capital</t>
-        </is>
-      </c>
-      <c r="C70" t="inlineStr">
-        <is>
-          <t>Changes in non-cash working capital total</t>
-        </is>
-      </c>
-      <c r="D70" t="inlineStr"/>
-      <c r="E70" s="5" t="n">
-        <v>-0.260222</v>
-      </c>
-    </row>
-    <row r="71">
-      <c r="A71" t="inlineStr">
-        <is>
-          <t>income_statement</t>
-        </is>
-      </c>
-      <c r="B71" t="inlineStr">
-        <is>
-          <t>Cash used in investing activities</t>
-        </is>
-      </c>
-      <c r="C71" t="inlineStr">
-        <is>
-          <t>Purchase of royalty interests 2</t>
-        </is>
-      </c>
-      <c r="D71" t="inlineStr"/>
-      <c r="E71" s="5" t="n">
-        <v>-1.6384</v>
-      </c>
-    </row>
-    <row r="72">
-      <c r="A72" t="inlineStr">
-        <is>
-          <t>income_statement</t>
-        </is>
-      </c>
-      <c r="B72" t="inlineStr">
-        <is>
-          <t>Cash used in investing activities</t>
-        </is>
-      </c>
-      <c r="C72" t="inlineStr">
-        <is>
-          <t>Cash used in investing activities total</t>
-        </is>
-      </c>
-      <c r="D72" t="inlineStr"/>
-      <c r="E72" s="5" t="n">
-        <v>-1.6384</v>
-      </c>
-    </row>
-    <row r="73">
-      <c r="A73" t="inlineStr">
-        <is>
-          <t>income_statement</t>
-        </is>
-      </c>
-      <c r="B73" t="inlineStr">
-        <is>
-          <t>Cash from financing activities</t>
-        </is>
-      </c>
-      <c r="C73" t="inlineStr">
-        <is>
-          <t>Proceeds from Capital Contribution 2</t>
-        </is>
-      </c>
-      <c r="D73" t="inlineStr"/>
-      <c r="E73" s="5" t="n">
-        <v>3.097188</v>
-      </c>
-    </row>
-    <row r="74">
-      <c r="A74" t="inlineStr">
-        <is>
-          <t>income_statement</t>
-        </is>
-      </c>
-      <c r="B74" t="inlineStr">
-        <is>
-          <t>Cash from financing activities</t>
-        </is>
-      </c>
-      <c r="C74" t="inlineStr">
-        <is>
-          <t>Proceeds from exercises of stock options</t>
-        </is>
-      </c>
-      <c r="D74" t="inlineStr"/>
-      <c r="E74" s="5" t="n">
-        <v>0.147095</v>
-      </c>
-    </row>
-    <row r="75">
-      <c r="A75" t="inlineStr">
-        <is>
-          <t>income_statement</t>
-        </is>
-      </c>
-      <c r="B75" t="inlineStr">
-        <is>
-          <t>Cash from financing activities</t>
-        </is>
-      </c>
-      <c r="C75" t="inlineStr">
-        <is>
-          <t>Cash from financing activities total</t>
-        </is>
-      </c>
-      <c r="D75" t="inlineStr"/>
-      <c r="E75" s="5" t="n">
-        <v>3.244283</v>
-      </c>
-    </row>
-    <row r="76">
-      <c r="A76" t="inlineStr">
-        <is>
-          <t>income_statement</t>
-        </is>
-      </c>
-      <c r="B76" t="inlineStr">
-        <is>
-          <t>Cash from financing activities</t>
-        </is>
-      </c>
-      <c r="C76" t="inlineStr">
-        <is>
-          <t>Effect of foreign exchange rate change on cash</t>
-        </is>
-      </c>
-      <c r="D76" t="inlineStr"/>
-      <c r="E76" s="5" t="n">
-        <v>0.026792</v>
-      </c>
-    </row>
-    <row r="77">
-      <c r="A77" t="inlineStr">
-        <is>
-          <t>income_statement</t>
-        </is>
-      </c>
-      <c r="B77" t="inlineStr">
-        <is>
-          <t>Cash from financing activities</t>
-        </is>
-      </c>
-      <c r="C77" t="inlineStr">
-        <is>
-          <t>Increase in cash during period</t>
-        </is>
-      </c>
-      <c r="D77" t="inlineStr"/>
-      <c r="E77" s="5" t="n">
-        <v>1.372453</v>
-      </c>
-    </row>
-    <row r="78">
-      <c r="A78" t="inlineStr">
-        <is>
-          <t>income_statement</t>
-        </is>
-      </c>
-      <c r="B78" t="inlineStr">
-        <is>
-          <t>Cash from financing activities</t>
-        </is>
-      </c>
-      <c r="C78" t="inlineStr">
-        <is>
-          <t>Cash, July 14, 2025</t>
-        </is>
-      </c>
-      <c r="D78" t="inlineStr"/>
-      <c r="E78" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-    </row>
-    <row r="79">
-      <c r="A79" t="inlineStr">
-        <is>
-          <t>income_statement</t>
-        </is>
-      </c>
-      <c r="B79" t="inlineStr">
-        <is>
-          <t>Cash from financing activities</t>
-        </is>
-      </c>
-      <c r="C79" t="inlineStr">
-        <is>
-          <t>Cash, end of the year</t>
-        </is>
-      </c>
-      <c r="D79" t="inlineStr"/>
-      <c r="E79" s="5" t="n">
-        <v>1.372453</v>
-      </c>
-    </row>
-    <row r="80">
-      <c r="A80" t="inlineStr">
-        <is>
-          <t>income_statement</t>
-        </is>
-      </c>
-      <c r="B80" t="inlineStr">
-        <is>
-          <t>Non-cash financing activities</t>
-        </is>
-      </c>
-      <c r="C80" t="inlineStr">
-        <is>
-          <t>Transfer of contributed surplus on exercise of options</t>
-        </is>
-      </c>
-      <c r="D80" t="inlineStr"/>
-      <c r="E80" s="5" t="n">
-        <v>0.013035</v>
-      </c>
-    </row>
-    <row r="81">
-      <c r="A81" t="inlineStr">
-        <is>
-          <t>income_statement</t>
-        </is>
-      </c>
-      <c r="B81" t="inlineStr">
-        <is>
-          <t>Shares issued relating to the Capital</t>
-        </is>
-      </c>
-      <c r="C81" t="inlineStr">
-        <is>
-          <t>Contribution 2 13,370,107 3,097,188 - - -</t>
-        </is>
-      </c>
-      <c r="D81" t="inlineStr"/>
-      <c r="E81" s="5" t="n">
-        <v>3.097188</v>
-      </c>
-    </row>
-    <row r="82">
-      <c r="A82" t="inlineStr">
-        <is>
-          <t>income_statement</t>
-        </is>
-      </c>
-      <c r="B82" t="inlineStr">
-        <is>
-          <t>Shares issued relating to the Capital</t>
-        </is>
-      </c>
-      <c r="C82" t="inlineStr">
-        <is>
-          <t>Shares issued relating to the Arrangement 2 53,816,239 - - - -</t>
-        </is>
-      </c>
-      <c r="D82" t="inlineStr"/>
-      <c r="E82" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-    </row>
-    <row r="83">
-      <c r="A83" t="inlineStr">
-        <is>
-          <t>income_statement</t>
-        </is>
-      </c>
-      <c r="B83" t="inlineStr">
-        <is>
-          <t>Shares issued relating to the Capital</t>
-        </is>
-      </c>
-      <c r="C83" t="inlineStr">
-        <is>
-          <t>Share-based compensation 6 - - 24,233 - -</t>
-        </is>
-      </c>
-      <c r="D83" t="inlineStr"/>
-      <c r="E83" s="5" t="n">
-        <v>0.024233</v>
-      </c>
-    </row>
-    <row r="84">
-      <c r="A84" t="inlineStr">
-        <is>
-          <t>income_statement</t>
-        </is>
-      </c>
-      <c r="B84" t="inlineStr">
-        <is>
-          <t>Shares issued relating to the Capital</t>
-        </is>
-      </c>
-      <c r="C84" t="inlineStr">
-        <is>
-          <t>Exercise of options 6 3,161,169 160,130 (13,035) - -</t>
-        </is>
-      </c>
-      <c r="D84" t="inlineStr"/>
-      <c r="E84" s="5" t="n">
-        <v>0.147095</v>
-      </c>
-    </row>
-    <row r="85">
-      <c r="A85" t="inlineStr">
-        <is>
-          <t>income_statement</t>
-        </is>
-      </c>
-      <c r="B85" t="inlineStr">
-        <is>
-          <t>Shares issued relating to the Capital</t>
-        </is>
-      </c>
-      <c r="C85" t="inlineStr">
-        <is>
-          <t>Comprehensive (loss) income for the period - - - (478,240) 73,365</t>
-        </is>
-      </c>
-      <c r="D85" t="inlineStr"/>
-      <c r="E85" s="5" t="n">
-        <v>-0.404875</v>
-      </c>
-    </row>
-    <row r="86">
-      <c r="A86" t="inlineStr">
-        <is>
-          <t>income_statement</t>
-        </is>
-      </c>
-      <c r="B86" t="inlineStr">
-        <is>
-          <t>Shares issued relating to the Capital</t>
-        </is>
-      </c>
-      <c r="C86" t="inlineStr">
-        <is>
-          <t>Ending balance, December 31, 2025 70,347,515 $3,257,318 $11,198 ($478,240) $73,365</t>
-        </is>
-      </c>
-      <c r="D86" t="inlineStr"/>
-      <c r="E86" s="5" t="n">
-        <v>2.863641</v>
       </c>
     </row>
   </sheetData>

--- a/output/pdf_financials_xlsx/LUNR.xlsx
+++ b/output/pdf_financials_xlsx/LUNR.xlsx
@@ -431,6 +431,10 @@
   </sheetPr>
   <dimension ref="A1:B135"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="56" customWidth="1" min="1" max="1"/>
+    <col width="18" customWidth="1" min="2" max="2"/>
+  </cols>
   <sheetData>
     <row r="1">
       <c r="A1" s="1" t="inlineStr">

--- a/output/pdf_financials_xlsx/LUNR.xlsx
+++ b/output/pdf_financials_xlsx/LUNR.xlsx
@@ -519,7 +519,7 @@
         </is>
       </c>
       <c r="B9" s="3" t="n">
-        <v>0</v>
+        <v>0.294767</v>
       </c>
     </row>
     <row r="10">
@@ -529,7 +529,7 @@
         </is>
       </c>
       <c r="B10" s="3" t="n">
-        <v>0.059385</v>
+        <v>0.354152</v>
       </c>
     </row>
     <row r="11">
@@ -539,7 +539,7 @@
         </is>
       </c>
       <c r="B11" s="3" t="n">
-        <v>-0.059385</v>
+        <v>0.468554</v>
       </c>
     </row>
     <row r="12">
@@ -559,7 +559,7 @@
         </is>
       </c>
       <c r="B13" s="3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
     </row>
     <row r="14">
@@ -599,7 +599,7 @@
         </is>
       </c>
       <c r="B17" s="3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
     </row>
     <row r="18">
@@ -1805,7 +1805,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E47"/>
+  <dimension ref="A1:E52"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="16" customWidth="1" min="1" max="1"/>
@@ -2598,114 +2598,106 @@
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>income_statement</t>
+          <t>cash_flow</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>General and administration</t>
+          <t>Non-cash financing activities</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>Listing and filing fees</t>
+          <t>Totalshareholders’equity $- 3,097,188 -24,233147,095(404,875)</t>
         </is>
       </c>
       <c r="D34" t="inlineStr"/>
       <c r="E34" s="5" t="n">
-        <v>0.19726</v>
+        <v>2.863641</v>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>income_statement</t>
+          <t>cash_flow</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>General and administration</t>
+          <t>Non-cash financing activities</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>Office and general</t>
-        </is>
-      </c>
-      <c r="D35" t="inlineStr">
-        <is>
-          <t>SellingGeneralAndAdministration</t>
-        </is>
-      </c>
+          <t>Accumulatedothercomprehensiveincome $- - ---73,365</t>
+        </is>
+      </c>
+      <c r="D35" t="inlineStr"/>
       <c r="E35" s="5" t="n">
-        <v>0.048817</v>
+        <v>0.073365</v>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>income_statement</t>
+          <t>cash_flow</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>General and administration</t>
+          <t>Non-cash financing activities</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>Professional fees</t>
-        </is>
-      </c>
-      <c r="D36" t="inlineStr">
-        <is>
-          <t>ProfessionalExpenseAndContractServicesExpense</t>
-        </is>
-      </c>
+          <t>Deficit $- - ---(478,240)</t>
+        </is>
+      </c>
+      <c r="D36" t="inlineStr"/>
       <c r="E36" s="5" t="n">
-        <v>0.06268</v>
+        <v>-0.47824</v>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>income_statement</t>
+          <t>cash_flow</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>General and administration</t>
+          <t>Non-cash financing activities</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>Promotion and public relations</t>
+          <t>Contributedsurplus $- - -24,233(13,035)-</t>
         </is>
       </c>
       <c r="D37" t="inlineStr"/>
       <c r="E37" s="5" t="n">
-        <v>0.027489</v>
+        <v>0.011198</v>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>income_statement</t>
+          <t>cash_flow</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>General and administration</t>
+          <t>Non-cash financing activities</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>Salaries and benefits</t>
+          <t>Inc.) shares 13,370,107 53,816,239 3,161,169 financial Number</t>
         </is>
       </c>
       <c r="D38" t="inlineStr"/>
       <c r="E38" s="5" t="n">
-        <v>0.097507</v>
+        <v>70.347515</v>
       </c>
     </row>
     <row r="39">
@@ -2721,12 +2713,16 @@
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>Share-based compensation</t>
-        </is>
-      </c>
-      <c r="D39" t="inlineStr"/>
+          <t>Listing and filing fees</t>
+        </is>
+      </c>
+      <c r="D39" t="inlineStr">
+        <is>
+          <t>OtherOperatingExpenses</t>
+        </is>
+      </c>
       <c r="E39" s="5" t="n">
-        <v>0.024233</v>
+        <v>0.19726</v>
       </c>
     </row>
     <row r="40">
@@ -2742,7 +2738,7 @@
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>Travel</t>
+          <t>Office and general</t>
         </is>
       </c>
       <c r="D40" t="inlineStr">
@@ -2751,7 +2747,7 @@
         </is>
       </c>
       <c r="E40" s="5" t="n">
-        <v>0.010568</v>
+        <v>0.048817</v>
       </c>
     </row>
     <row r="41">
@@ -2767,12 +2763,16 @@
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>Operating loss</t>
-        </is>
-      </c>
-      <c r="D41" t="inlineStr"/>
+          <t>Professional fees</t>
+        </is>
+      </c>
+      <c r="D41" t="inlineStr">
+        <is>
+          <t>ProfessionalExpenseAndContractServicesExpense</t>
+        </is>
+      </c>
       <c r="E41" s="5" t="n">
-        <v>0.468554</v>
+        <v>0.06268</v>
       </c>
     </row>
     <row r="42">
@@ -2783,21 +2783,17 @@
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>Other expenses</t>
+          <t>General and administration</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>Foreign exchange loss</t>
-        </is>
-      </c>
-      <c r="D42" t="inlineStr">
-        <is>
-          <t>OtherIncomeExpense</t>
-        </is>
-      </c>
+          <t>Promotion and public relations</t>
+        </is>
+      </c>
+      <c r="D42" t="inlineStr"/>
       <c r="E42" s="5" t="n">
-        <v>0.009686</v>
+        <v>0.027489</v>
       </c>
     </row>
     <row r="43">
@@ -2808,21 +2804,21 @@
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>Other expenses</t>
+          <t>General and administration</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>Net loss</t>
+          <t>Salaries and benefits</t>
         </is>
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>NetIncome</t>
+          <t>OtherOperatingExpenses</t>
         </is>
       </c>
       <c r="E43" s="5" t="n">
-        <v>0.47824</v>
+        <v>0.097507</v>
       </c>
     </row>
     <row r="44">
@@ -2833,17 +2829,17 @@
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>Other comprehensive (income)</t>
+          <t>General and administration</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>Currency translation adjustment</t>
+          <t>Share-based compensation</t>
         </is>
       </c>
       <c r="D44" t="inlineStr"/>
       <c r="E44" s="5" t="n">
-        <v>-0.073365</v>
+        <v>0.024233</v>
       </c>
     </row>
     <row r="45">
@@ -2854,17 +2850,21 @@
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>Other comprehensive (income)</t>
+          <t>General and administration</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>Comprehensive loss</t>
-        </is>
-      </c>
-      <c r="D45" t="inlineStr"/>
+          <t>Travel</t>
+        </is>
+      </c>
+      <c r="D45" t="inlineStr">
+        <is>
+          <t>SellingGeneralAndAdministration</t>
+        </is>
+      </c>
       <c r="E45" s="5" t="n">
-        <v>0.404875</v>
+        <v>0.010568</v>
       </c>
     </row>
     <row r="46">
@@ -2875,21 +2875,21 @@
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>Other comprehensive (income)</t>
+          <t>General and administration</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>Basic and diluted loss per common share</t>
+          <t>Operating loss</t>
         </is>
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>BasicEPS</t>
+          <t>OperatingIncome</t>
         </is>
       </c>
       <c r="E46" s="5" t="n">
-        <v>2e-08</v>
+        <v>0.468554</v>
       </c>
     </row>
     <row r="47">
@@ -2900,20 +2900,137 @@
       </c>
       <c r="B47" t="inlineStr">
         <is>
+          <t>Other expenses</t>
+        </is>
+      </c>
+      <c r="C47" t="inlineStr">
+        <is>
+          <t>Foreign exchange loss</t>
+        </is>
+      </c>
+      <c r="D47" t="inlineStr">
+        <is>
+          <t>OtherIncomeExpense</t>
+        </is>
+      </c>
+      <c r="E47" s="5" t="n">
+        <v>0.009686</v>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" t="inlineStr">
+        <is>
+          <t>income_statement</t>
+        </is>
+      </c>
+      <c r="B48" t="inlineStr">
+        <is>
+          <t>Other expenses</t>
+        </is>
+      </c>
+      <c r="C48" t="inlineStr">
+        <is>
+          <t>Net loss</t>
+        </is>
+      </c>
+      <c r="D48" t="inlineStr">
+        <is>
+          <t>NetIncome</t>
+        </is>
+      </c>
+      <c r="E48" s="5" t="n">
+        <v>0.47824</v>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" t="inlineStr">
+        <is>
+          <t>income_statement</t>
+        </is>
+      </c>
+      <c r="B49" t="inlineStr">
+        <is>
           <t>Other comprehensive (income)</t>
         </is>
       </c>
-      <c r="C47" t="inlineStr">
+      <c r="C49" t="inlineStr">
+        <is>
+          <t>Currency translation adjustment</t>
+        </is>
+      </c>
+      <c r="D49" t="inlineStr"/>
+      <c r="E49" s="5" t="n">
+        <v>-0.073365</v>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" t="inlineStr">
+        <is>
+          <t>income_statement</t>
+        </is>
+      </c>
+      <c r="B50" t="inlineStr">
+        <is>
+          <t>Other comprehensive (income)</t>
+        </is>
+      </c>
+      <c r="C50" t="inlineStr">
+        <is>
+          <t>Comprehensive loss</t>
+        </is>
+      </c>
+      <c r="D50" t="inlineStr"/>
+      <c r="E50" s="5" t="n">
+        <v>0.404875</v>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" t="inlineStr">
+        <is>
+          <t>income_statement</t>
+        </is>
+      </c>
+      <c r="B51" t="inlineStr">
+        <is>
+          <t>Other comprehensive (income)</t>
+        </is>
+      </c>
+      <c r="C51" t="inlineStr">
+        <is>
+          <t>Basic and diluted loss per common share</t>
+        </is>
+      </c>
+      <c r="D51" t="inlineStr">
+        <is>
+          <t>BasicEPS</t>
+        </is>
+      </c>
+      <c r="E51" s="5" t="n">
+        <v>2e-08</v>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" t="inlineStr">
+        <is>
+          <t>income_statement</t>
+        </is>
+      </c>
+      <c r="B52" t="inlineStr">
+        <is>
+          <t>Other comprehensive (income)</t>
+        </is>
+      </c>
+      <c r="C52" t="inlineStr">
         <is>
           <t>Weighted average common shares outstanding</t>
         </is>
       </c>
-      <c r="D47" t="inlineStr">
+      <c r="D52" t="inlineStr">
         <is>
           <t>SharesOutstanding</t>
         </is>
       </c>
-      <c r="E47" s="5" t="n">
+      <c r="E52" s="5" t="n">
         <v>28.945492</v>
       </c>
     </row>

--- a/output/pdf_financials_xlsx/LUNR.xlsx
+++ b/output/pdf_financials_xlsx/LUNR.xlsx
@@ -589,7 +589,7 @@
         </is>
       </c>
       <c r="B16" s="3" t="n">
-        <v>0.47824</v>
+        <v>-0.47824</v>
       </c>
     </row>
     <row r="17">
@@ -633,7 +633,7 @@
         </is>
       </c>
       <c r="B20" s="3" t="n">
-        <v>0.47824</v>
+        <v>-0.47824</v>
       </c>
     </row>
     <row r="21">
@@ -663,7 +663,7 @@
         </is>
       </c>
       <c r="B23" s="3" t="n">
-        <v>0.47824</v>
+        <v>-0.47824</v>
       </c>
     </row>
     <row r="24">
@@ -693,7 +693,7 @@
         </is>
       </c>
       <c r="B26" s="3" t="n">
-        <v>23.912</v>
+        <v>-23.912</v>
       </c>
     </row>
     <row r="27">
@@ -703,7 +703,7 @@
         </is>
       </c>
       <c r="B27" s="3" t="n">
-        <v>0.47824</v>
+        <v>-0.47824</v>
       </c>
     </row>
     <row r="28">
@@ -723,7 +723,7 @@
         </is>
       </c>
       <c r="B29" s="3" t="n">
-        <v>0.47824</v>
+        <v>-0.47824</v>
       </c>
     </row>
     <row r="30">
@@ -745,7 +745,7 @@
         </is>
       </c>
       <c r="B31" s="3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
     </row>
     <row r="32">
@@ -2939,7 +2939,7 @@
         </is>
       </c>
       <c r="E48" s="5" t="n">
-        <v>0.47824</v>
+        <v>-0.47824</v>
       </c>
     </row>
     <row r="49">

--- a/output/pdf_financials_xlsx/LUNR.xlsx
+++ b/output/pdf_financials_xlsx/LUNR.xlsx
@@ -774,7 +774,7 @@
         </is>
       </c>
       <c r="B34" s="3" t="n">
-        <v>0</v>
+        <v>1.372453</v>
       </c>
     </row>
     <row r="35">
@@ -794,7 +794,7 @@
         </is>
       </c>
       <c r="B36" s="3" t="n">
-        <v>0</v>
+        <v>1.372453</v>
       </c>
     </row>
     <row r="37">
@@ -914,7 +914,7 @@
         </is>
       </c>
       <c r="B48" s="3" t="n">
-        <v>1.426262</v>
+        <v>0.053809</v>
       </c>
     </row>
     <row r="49">
@@ -1859,7 +1859,7 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>Cash</t>
+          <t>CashAndCashEquivalents</t>
         </is>
       </c>
       <c r="E2" s="5" t="n">
